--- a/final_data_pipeline/output/322110_kraft_elec.xlsx
+++ b/final_data_pipeline/output/322110_kraft_elec.xlsx
@@ -789,7 +789,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="L5">
         <v>8000</v>
@@ -810,10 +810,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R5">
-        <v>1.800714285714286</v>
+        <v>1.975772235794973</v>
       </c>
       <c r="S5">
-        <v>1.963947368421052</v>
+        <v>2.177153507468733</v>
       </c>
       <c r="T5">
         <v>10.84733831532546</v>
@@ -848,7 +848,7 @@
         <v>49</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="L6">
         <v>8000</v>
@@ -863,10 +863,10 @@
         <v>147576.5701483236</v>
       </c>
       <c r="R6">
-        <v>1.280428571428571</v>
+        <v>1.352319749654237</v>
       </c>
       <c r="S6">
-        <v>1.342878787878788</v>
+        <v>1.423118895050623</v>
       </c>
       <c r="T6">
         <v>18.44707126854045</v>
@@ -901,7 +901,7 @@
         <v>50</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="L7">
         <v>8000</v>
@@ -1119,7 +1119,7 @@
         <v>70</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L11">
         <v>8000</v>
@@ -1140,10 +1140,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R11">
-        <v>1.800714285714286</v>
+        <v>1.847705673092716</v>
       </c>
       <c r="S11">
-        <v>1.963947368421052</v>
+        <v>2.020749367497032</v>
       </c>
       <c r="T11">
         <v>90.99833177426738</v>
@@ -1178,7 +1178,7 @@
         <v>49</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L12">
         <v>8000</v>
@@ -1193,10 +1193,10 @@
         <v>1238019.99182531</v>
       </c>
       <c r="R12">
-        <v>1.280428571428571</v>
+        <v>1.300269876134972</v>
       </c>
       <c r="S12">
-        <v>1.342878787878788</v>
+        <v>1.364969709970879</v>
       </c>
       <c r="T12">
         <v>154.7524989781637</v>
@@ -1231,7 +1231,7 @@
         <v>50</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1278,7 +1278,7 @@
         <v>50</v>
       </c>
       <c r="K14">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="L14">
         <v>8000</v>
@@ -1325,7 +1325,7 @@
         <v>49</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="L15">
         <v>8000</v>
@@ -1340,10 +1340,10 @@
         <v>1817801.447711399</v>
       </c>
       <c r="R15">
-        <v>1.280428571428571</v>
+        <v>1.304077921028169</v>
       </c>
       <c r="S15">
-        <v>1.342878787878788</v>
+        <v>1.369214264257821</v>
       </c>
       <c r="T15">
         <v>227.2251809639249</v>
@@ -1384,7 +1384,7 @@
         <v>70</v>
       </c>
       <c r="K16">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="L16">
         <v>8000</v>
@@ -1405,10 +1405,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R16">
-        <v>1.800714285714286</v>
+        <v>1.856836936506854</v>
       </c>
       <c r="S16">
-        <v>1.963947368421052</v>
+        <v>2.031823338122968</v>
       </c>
       <c r="T16">
         <v>133.6140775842387</v>
@@ -1443,7 +1443,7 @@
         <v>49</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>12.92654320987656</v>
       </c>
       <c r="L17">
         <v>8000</v>
@@ -1458,10 +1458,10 @@
         <v>1454870.092303158</v>
       </c>
       <c r="R17">
-        <v>1.280428571428571</v>
+        <v>1.302205489329493</v>
       </c>
       <c r="S17">
-        <v>1.342878787878788</v>
+        <v>1.367127007643996</v>
       </c>
       <c r="T17">
         <v>181.8587615378948</v>
@@ -1496,7 +1496,7 @@
         <v>50</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>12.92654320987656</v>
       </c>
       <c r="L18">
         <v>8000</v>
@@ -1549,7 +1549,7 @@
         <v>70</v>
       </c>
       <c r="K19">
-        <v>10</v>
+        <v>12.92654320987656</v>
       </c>
       <c r="L19">
         <v>8000</v>
@@ -1570,10 +1570,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R19">
-        <v>1.800714285714286</v>
+        <v>1.852342479090948</v>
       </c>
       <c r="S19">
-        <v>1.963947368421052</v>
+        <v>2.026371187792892</v>
       </c>
       <c r="T19">
         <v>106.9374906883917</v>
@@ -1614,7 +1614,7 @@
         <v>70</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L20">
         <v>8000</v>
@@ -1635,10 +1635,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R20">
-        <v>1.800714285714286</v>
+        <v>1.626775542720574</v>
       </c>
       <c r="S20">
-        <v>1.963947368421052</v>
+        <v>1.756382654173023</v>
       </c>
       <c r="T20">
         <v>143.8382082628356</v>
@@ -1673,7 +1673,7 @@
         <v>50</v>
       </c>
       <c r="K21">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L21">
         <v>8000</v>
@@ -1720,7 +1720,7 @@
         <v>49</v>
       </c>
       <c r="K22">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L22">
         <v>8000</v>
@@ -1735,10 +1735,10 @@
         <v>1956899.362281267</v>
       </c>
       <c r="R22">
-        <v>1.280428571428571</v>
+        <v>1.203236793039155</v>
       </c>
       <c r="S22">
-        <v>1.342878787878788</v>
+        <v>1.257328254301852</v>
       </c>
       <c r="T22">
         <v>244.6124202851584</v>
@@ -1773,7 +1773,7 @@
         <v>49</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L23">
         <v>8000</v>
@@ -1788,10 +1788,10 @@
         <v>2899569.172373784</v>
       </c>
       <c r="R23">
-        <v>1.280428571428571</v>
+        <v>1.302881541082627</v>
       </c>
       <c r="S23">
-        <v>1.342878787878788</v>
+        <v>1.367880580392128</v>
       </c>
       <c r="T23">
         <v>362.446146546723</v>
@@ -1826,7 +1826,7 @@
         <v>50</v>
       </c>
       <c r="K24">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L24">
         <v>8000</v>
@@ -1879,7 +1879,7 @@
         <v>70</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L25">
         <v>8000</v>
@@ -1900,10 +1900,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R25">
-        <v>1.800714285714286</v>
+        <v>1.853964204859962</v>
       </c>
       <c r="S25">
-        <v>1.963947368421052</v>
+        <v>2.02833814451736</v>
       </c>
       <c r="T25">
         <v>213.1273802461655</v>
@@ -2103,7 +2103,7 @@
         <v>50</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L29">
         <v>8000</v>
@@ -2156,7 +2156,7 @@
         <v>70</v>
       </c>
       <c r="K30">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L30">
         <v>8000</v>
@@ -2177,10 +2177,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R30">
-        <v>1.800714285714286</v>
+        <v>1.672133966590239</v>
       </c>
       <c r="S30">
-        <v>1.963947368421052</v>
+        <v>1.810106000718649</v>
       </c>
       <c r="T30">
         <v>147.3449140348732</v>
@@ -2215,7 +2215,7 @@
         <v>49</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="L31">
         <v>8000</v>
@@ -2230,10 +2230,10 @@
         <v>2004607.619856812</v>
       </c>
       <c r="R31">
-        <v>1.280428571428571</v>
+        <v>1.223958122597613</v>
       </c>
       <c r="S31">
-        <v>1.342878787878788</v>
+        <v>1.280232184891932</v>
       </c>
       <c r="T31">
         <v>250.5759524821015</v>
@@ -2268,7 +2268,7 @@
         <v>50</v>
       </c>
       <c r="K32">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L32">
         <v>8000</v>
@@ -2315,7 +2315,7 @@
         <v>49</v>
       </c>
       <c r="K33">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L33">
         <v>8000</v>
@@ -2330,10 +2330,10 @@
         <v>623726.120738358</v>
       </c>
       <c r="R33">
-        <v>1.280428571428571</v>
+        <v>1.199420117463385</v>
       </c>
       <c r="S33">
-        <v>1.342878787878788</v>
+        <v>1.253114445055376</v>
       </c>
       <c r="T33">
         <v>77.96576509229475</v>
@@ -2374,7 +2374,7 @@
         <v>70</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L34">
         <v>8000</v>
@@ -2395,10 +2395,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R34">
-        <v>1.800714285714286</v>
+        <v>1.618523362263702</v>
       </c>
       <c r="S34">
-        <v>1.963947368421052</v>
+        <v>1.746638928617865</v>
       </c>
       <c r="T34">
         <v>45.84581577519039</v>
@@ -2433,7 +2433,7 @@
         <v>49</v>
       </c>
       <c r="K35">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L35">
         <v>8000</v>
@@ -2448,10 +2448,10 @@
         <v>356742.7347757882</v>
       </c>
       <c r="R35">
-        <v>1.280428571428571</v>
+        <v>1.302881541082627</v>
       </c>
       <c r="S35">
-        <v>1.342878787878788</v>
+        <v>1.367880580392128</v>
       </c>
       <c r="T35">
         <v>44.59284184697353</v>
@@ -2492,7 +2492,7 @@
         <v>70</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L36">
         <v>8000</v>
@@ -2513,10 +2513,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R36">
-        <v>1.800714285714286</v>
+        <v>1.853964204859962</v>
       </c>
       <c r="S36">
-        <v>1.963947368421052</v>
+        <v>2.02833814451736</v>
       </c>
       <c r="T36">
         <v>26.22170397210139</v>
@@ -2551,7 +2551,7 @@
         <v>50</v>
       </c>
       <c r="K37">
-        <v>10</v>
+        <v>13.0158303464755</v>
       </c>
       <c r="L37">
         <v>8000</v>
@@ -2598,7 +2598,7 @@
         <v>50</v>
       </c>
       <c r="K38">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L38">
         <v>8000</v>
@@ -2645,7 +2645,7 @@
         <v>49</v>
       </c>
       <c r="K39">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L39">
         <v>8000</v>
@@ -2660,10 +2660,10 @@
         <v>646698.137479772</v>
       </c>
       <c r="R39">
-        <v>1.280428571428571</v>
+        <v>1.248232108317215</v>
       </c>
       <c r="S39">
-        <v>1.342878787878788</v>
+        <v>1.307120032773454</v>
       </c>
       <c r="T39">
         <v>80.83726718497149</v>
@@ -2704,7 +2704,7 @@
         <v>70</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="L40">
         <v>8000</v>
@@ -2725,10 +2725,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R40">
-        <v>1.800714285714286</v>
+        <v>1.726493341788205</v>
       </c>
       <c r="S40">
-        <v>1.963947368421052</v>
+        <v>1.874863921842289</v>
       </c>
       <c r="T40">
         <v>47.53433067378839</v>
@@ -2928,7 +2928,7 @@
         <v>50</v>
       </c>
       <c r="K44">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L44">
         <v>8000</v>
@@ -2981,7 +2981,7 @@
         <v>70</v>
       </c>
       <c r="K45">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L45">
         <v>8000</v>
@@ -3002,10 +3002,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R45">
-        <v>1.800714285714286</v>
+        <v>1.626775542720574</v>
       </c>
       <c r="S45">
-        <v>1.963947368421052</v>
+        <v>1.756382654173023</v>
       </c>
       <c r="T45">
         <v>9.248763282758299</v>
@@ -3040,7 +3040,7 @@
         <v>49</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>-1.226851851851833</v>
       </c>
       <c r="L46">
         <v>8000</v>
@@ -3055,10 +3055,10 @@
         <v>125828.1731155048</v>
       </c>
       <c r="R46">
-        <v>1.280428571428571</v>
+        <v>1.203236793039155</v>
       </c>
       <c r="S46">
-        <v>1.342878787878788</v>
+        <v>1.257328254301852</v>
       </c>
       <c r="T46">
         <v>15.72852163943809</v>
@@ -3093,7 +3093,7 @@
         <v>49</v>
       </c>
       <c r="K47">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L47">
         <v>8000</v>
@@ -3108,10 +3108,10 @@
         <v>1178282.823453274</v>
       </c>
       <c r="R47">
-        <v>1.280428571428571</v>
+        <v>1.233817681248088</v>
       </c>
       <c r="S47">
-        <v>1.342878787878788</v>
+        <v>1.291146001942376</v>
       </c>
       <c r="T47">
         <v>147.2853529316593</v>
@@ -3152,7 +3152,7 @@
         <v>70</v>
       </c>
       <c r="K48">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L48">
         <v>8000</v>
@@ -3173,10 +3173,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R48">
-        <v>1.800714285714286</v>
+        <v>1.694051767048283</v>
       </c>
       <c r="S48">
-        <v>1.963947368421052</v>
+        <v>1.836167304537999</v>
       </c>
       <c r="T48">
         <v>86.60746353088865</v>
@@ -3211,7 +3211,7 @@
         <v>50</v>
       </c>
       <c r="K49">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="L49">
         <v>8000</v>
@@ -3594,7 +3594,7 @@
         <v>70</v>
       </c>
       <c r="K56">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L56">
         <v>8000</v>
@@ -3615,10 +3615,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R56">
-        <v>1.800714285714286</v>
+        <v>1.92665172779809</v>
       </c>
       <c r="S56">
-        <v>1.963947368421052</v>
+        <v>2.116885095206829</v>
       </c>
       <c r="T56">
         <v>10.45519630532747</v>
@@ -3653,7 +3653,7 @@
         <v>49</v>
       </c>
       <c r="K57">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L57">
         <v>8000</v>
@@ -3668,10 +3668,10 @@
         <v>142241.5311586379</v>
       </c>
       <c r="R57">
-        <v>1.280428571428571</v>
+        <v>1.332696358504853</v>
       </c>
       <c r="S57">
-        <v>1.342878787878788</v>
+        <v>1.401162263046183</v>
       </c>
       <c r="T57">
         <v>17.78019139482974</v>
@@ -3706,7 +3706,7 @@
         <v>50</v>
       </c>
       <c r="K58">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="L58">
         <v>8000</v>
